--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_19.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_19.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5532910808522076</v>
+        <v>0.7477882017654199</v>
       </c>
       <c r="C2">
-        <v>0.0134692947956605</v>
+        <v>-0.7687694535957467</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.273575243918213</v>
+        <v>-0.6066293824144074</v>
       </c>
       <c r="C3">
-        <v>0.3441739435376184</v>
+        <v>0.3233185074997772</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.1218780060100644</v>
+        <v>1.694229189276123</v>
       </c>
       <c r="C4">
-        <v>0.1167513422609714</v>
+        <v>-0.7640130475806076</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.651434044937807</v>
+        <v>-0.3912003437681515</v>
       </c>
       <c r="C5">
-        <v>0.9249474933072244</v>
+        <v>-0.6790716650593035</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.06552536431393266</v>
+        <v>0.4943071513162889</v>
       </c>
       <c r="C6">
-        <v>-0.2518233951662712</v>
+        <v>1.199751031601942</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.6042906744483548</v>
+        <v>-0.8444916929719075</v>
       </c>
       <c r="C7">
-        <v>0.4710740404980537</v>
+        <v>-1.138252672049139</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.288740617053074</v>
+        <v>1.079388270886352</v>
       </c>
       <c r="C8">
-        <v>-1.627417273658305</v>
+        <v>1.136981651073532</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.3879401522997215</v>
+        <v>0.2987099511212968</v>
       </c>
       <c r="C9">
-        <v>0.9657181379727451</v>
+        <v>1.246056354354904</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.5176332871609103</v>
+        <v>-0.2281499073084336</v>
       </c>
       <c r="C10">
-        <v>0.1338135973154509</v>
+        <v>-1.186279415475679</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.5910765626657499</v>
+        <v>-0.2513668806529545</v>
       </c>
       <c r="C11">
-        <v>1.894131370269336</v>
+        <v>0.1998178661660743</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-1.436688723850448</v>
+        <v>-0.5652353889988143</v>
       </c>
       <c r="C12">
-        <v>-1.260726281562634</v>
+        <v>-1.569048486874792</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.2184158221628369</v>
+        <v>1.216699988348641</v>
       </c>
       <c r="C13">
-        <v>0.8034666732861554</v>
+        <v>0.06442998257693799</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.05990542965147021</v>
+        <v>0.2406810784048358</v>
       </c>
       <c r="C14">
-        <v>0.3034684533895121</v>
+        <v>-0.2201787342557881</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.3014779150981462</v>
+        <v>-2.221706289256282</v>
       </c>
       <c r="C15">
-        <v>-0.6113530864345338</v>
+        <v>-0.5875341595823712</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.8814267992634794</v>
+        <v>0.2756812926249438</v>
       </c>
       <c r="C16">
-        <v>-0.07273140305346415</v>
+        <v>-0.6347105170122113</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.03651594978208609</v>
+        <v>-0.3937420709337912</v>
       </c>
       <c r="C17">
-        <v>0.4521622034900709</v>
+        <v>0.4203538803073965</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.187431136963972</v>
+        <v>0.836468560475209</v>
       </c>
       <c r="C18">
-        <v>-1.419105098817805</v>
+        <v>0.9777714734951235</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.2737342403759819</v>
+        <v>1.383221862716802</v>
       </c>
       <c r="C19">
-        <v>-1.808451267204835</v>
+        <v>1.600032348032795</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.7417734323211156</v>
+        <v>-0.6498901913310362</v>
       </c>
       <c r="C20">
-        <v>0.5759774853653815</v>
+        <v>-1.933310754093996</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.8540621212484144</v>
+        <v>0.3947496256136889</v>
       </c>
       <c r="C21">
-        <v>-0.8034918229200934</v>
+        <v>-1.202467787853804</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.7275505154810061</v>
+        <v>0.4871606702625429</v>
       </c>
       <c r="C22">
-        <v>-1.421302037244101</v>
+        <v>0.1619214851541894</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.151530096153182</v>
+        <v>-0.7438576699144469</v>
       </c>
       <c r="C23">
-        <v>0.3728404467683488</v>
+        <v>-2.038728899900206</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.9088519865497864</v>
+        <v>0.1097909942427136</v>
       </c>
       <c r="C24">
-        <v>0.118579918520467</v>
+        <v>-1.025840289721582</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.09991927371927495</v>
+        <v>0.1612525742892809</v>
       </c>
       <c r="C25">
-        <v>-0.4668769377430094</v>
+        <v>0.3927652467127906</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-2.64699957026938</v>
+        <v>-0.5306047243828788</v>
       </c>
       <c r="C26">
-        <v>1.341095332903255</v>
+        <v>0.5744686498223801</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.2705867452590071</v>
+        <v>-1.132341742614511</v>
       </c>
       <c r="C27">
-        <v>0.2079796967728808</v>
+        <v>-0.9325670486282008</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>2.047828765526136</v>
+        <v>-0.125493547925248</v>
       </c>
       <c r="C28">
-        <v>-1.36655519000154</v>
+        <v>0.5195445305563929</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.06903603423086641</v>
+        <v>-1.125031748793153</v>
       </c>
       <c r="C29">
-        <v>1.338146943870957</v>
+        <v>-1.336853906859639</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.1428875444587498</v>
+        <v>-2.121317693641492</v>
       </c>
       <c r="C30">
-        <v>0.8394732490856529</v>
+        <v>0.3918607371258571</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.280019349217231</v>
+        <v>1.895555375062165</v>
       </c>
       <c r="C31">
-        <v>0.1778340613360377</v>
+        <v>-1.143355009431527</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.2015194961968851</v>
+        <v>-0.1048907869178519</v>
       </c>
       <c r="C32">
-        <v>-0.4192607896378845</v>
+        <v>-0.0629314664507836</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.6997912858042428</v>
+        <v>1.234992391053877</v>
       </c>
       <c r="C33">
-        <v>0.2615115664941723</v>
+        <v>0.6631123331117459</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.002459091401019964</v>
+        <v>-0.9385227566441451</v>
       </c>
       <c r="C34">
-        <v>1.084772400165235</v>
+        <v>-2.204187907686128</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.07122290568273447</v>
+        <v>0.5523035832619223</v>
       </c>
       <c r="C35">
-        <v>0.788386922130882</v>
+        <v>1.267543276008511</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.4979525190415311</v>
+        <v>-1.288866702894931</v>
       </c>
       <c r="C36">
-        <v>-1.294686486793096</v>
+        <v>0.756539936475041</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.1431657242733907</v>
+        <v>1.73256173019746</v>
       </c>
       <c r="C37">
-        <v>1.231243078307135</v>
+        <v>0.2451188300653694</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.65074211677112</v>
+        <v>0.07778668196693177</v>
       </c>
       <c r="C38">
-        <v>0.3697359628692993</v>
+        <v>1.471678779669218</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.189472823150498</v>
+        <v>-0.9860679315618921</v>
       </c>
       <c r="C39">
-        <v>-0.5652607755390451</v>
+        <v>1.007118169530654</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.261817814526539</v>
+        <v>1.545477998902216</v>
       </c>
       <c r="C40">
-        <v>-0.6908233333232926</v>
+        <v>1.12401685612507</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.612367664968732</v>
+        <v>0.7628795573041798</v>
       </c>
       <c r="C41">
-        <v>-0.358025769113233</v>
+        <v>0.3551282706638138</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.349758858919935</v>
+        <v>-2.121465253358456</v>
       </c>
       <c r="C42">
-        <v>-0.6588896089129488</v>
+        <v>-0.5523227051411917</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.2608287872205948</v>
+        <v>0.5444827718311742</v>
       </c>
       <c r="C43">
-        <v>0.3182731247011452</v>
+        <v>-0.73179812226802</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.450797593445671</v>
+        <v>-1.266093130803362</v>
       </c>
       <c r="C44">
-        <v>-0.06939210682686359</v>
+        <v>0.4984404449572143</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-1.184231580171397</v>
+        <v>0.05334771202418043</v>
       </c>
       <c r="C45">
-        <v>0.7841491079417575</v>
+        <v>-0.555966226619197</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.3955776872712057</v>
+        <v>-1.15919836080405</v>
       </c>
       <c r="C46">
-        <v>1.058164978316285</v>
+        <v>0.2910954923572414</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.4294530024319659</v>
+        <v>0.1432546454076167</v>
       </c>
       <c r="C47">
-        <v>-1.493537069869606</v>
+        <v>0.2726576710472679</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.3183439313696655</v>
+        <v>0.8043274094319618</v>
       </c>
       <c r="C48">
-        <v>-0.9521365566059516</v>
+        <v>0.6501624708220588</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.080059629543195</v>
+        <v>-0.4720257113619269</v>
       </c>
       <c r="C49">
-        <v>0.1897309395538303</v>
+        <v>-0.361757612314701</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5835885792891232</v>
+        <v>-1.608648276132571</v>
       </c>
       <c r="C50">
-        <v>-0.5982874162144445</v>
+        <v>0.3651846975463784</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.631369063696225</v>
+        <v>1.496996870105933</v>
       </c>
       <c r="C51">
-        <v>-1.39629228446816</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-1.161826331330272</v>
-      </c>
-      <c r="C52">
-        <v>1.261010869790916</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>0.3884963350408659</v>
-      </c>
-      <c r="C53">
-        <v>-0.3205799605716444</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>0.7586694594678941</v>
-      </c>
-      <c r="C54">
-        <v>-0.3085749579827181</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.1949790098989669</v>
-      </c>
-      <c r="C55">
-        <v>0.3266265952657073</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-0.1571701573797947</v>
-      </c>
-      <c r="C56">
-        <v>0.9012098358757634</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.4867621415689727</v>
-      </c>
-      <c r="C57">
-        <v>-1.120947657721406</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>0.04493630761953861</v>
-      </c>
-      <c r="C58">
-        <v>-0.623041296734694</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-1.302537014326018</v>
-      </c>
-      <c r="C59">
-        <v>2.39057331083822</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>-0.8630684181664079</v>
-      </c>
-      <c r="C60">
-        <v>-0.5903197615608833</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-0.7444860254946025</v>
-      </c>
-      <c r="C61">
-        <v>-1.052088474456714</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.9788587074821128</v>
-      </c>
-      <c r="C62">
-        <v>0.4091932766934968</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>-0.2324972045405974</v>
-      </c>
-      <c r="C63">
-        <v>0.5375908076156157</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.02572881350202339</v>
-      </c>
-      <c r="C64">
-        <v>-1.624895563975347</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.4142028332849527</v>
-      </c>
-      <c r="C65">
-        <v>0.2753490400590268</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.8107101917901791</v>
-      </c>
-      <c r="C66">
-        <v>-0.1282700558901793</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>0.1917958154027813</v>
-      </c>
-      <c r="C67">
-        <v>-0.115630616551867</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-0.5064551755657597</v>
-      </c>
-      <c r="C68">
-        <v>-0.2992150461651801</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.163471112997683</v>
-      </c>
-      <c r="C69">
-        <v>-1.350268613546117</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.6539102525999643</v>
-      </c>
-      <c r="C70">
-        <v>0.2161270597846197</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>1.166706985356371</v>
-      </c>
-      <c r="C71">
-        <v>-0.1584996180375698</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>0.5911387377647769</v>
-      </c>
-      <c r="C72">
-        <v>-0.1760495348492395</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.3863053497332378</v>
-      </c>
-      <c r="C73">
-        <v>0.3636285594280246</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.2592043687956015</v>
-      </c>
-      <c r="C74">
-        <v>-0.791606567511755</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>1.04854148721183</v>
-      </c>
-      <c r="C75">
-        <v>-0.865389871413196</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-0.3056752797880541</v>
-      </c>
-      <c r="C76">
-        <v>0.4491942654854825</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.4796233321487948</v>
-      </c>
-      <c r="C77">
-        <v>-0.5451900500644968</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-0.1816978478989814</v>
-      </c>
-      <c r="C78">
-        <v>-0.09820214876190313</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.6183941425862972</v>
-      </c>
-      <c r="C79">
-        <v>-1.316414503947997</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.01824720781693078</v>
-      </c>
-      <c r="C80">
-        <v>-0.5606792474014476</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.09993434764899563</v>
-      </c>
-      <c r="C81">
-        <v>-0.903079797060501</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>1.871673956902727</v>
-      </c>
-      <c r="C82">
-        <v>-0.7414337133135946</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-1.073569011811425</v>
-      </c>
-      <c r="C83">
-        <v>0.8153189125161682</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-1.037523174276886</v>
-      </c>
-      <c r="C84">
-        <v>1.331410619729756</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.961859976122491</v>
-      </c>
-      <c r="C85">
-        <v>0.6853141120892066</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-1.744488318618018</v>
-      </c>
-      <c r="C86">
-        <v>1.204576687517337</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>0.6046446674398289</v>
-      </c>
-      <c r="C87">
-        <v>-0.9134409021517594</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.3244969094424691</v>
-      </c>
-      <c r="C88">
-        <v>-0.9785199690968084</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-0.2482614730129473</v>
-      </c>
-      <c r="C89">
-        <v>-0.07859208422813407</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-0.004842627013407981</v>
-      </c>
-      <c r="C90">
-        <v>-0.829876198175679</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-1.119833639413804</v>
-      </c>
-      <c r="C91">
-        <v>1.93632915110741</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.3927914987067637</v>
-      </c>
-      <c r="C92">
-        <v>-0.5756996480383646</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-1.061309624131506</v>
-      </c>
-      <c r="C93">
-        <v>0.6250257641570003</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.4550240098111664</v>
-      </c>
-      <c r="C94">
-        <v>-0.609223051306797</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-0.7326801602684802</v>
-      </c>
-      <c r="C95">
-        <v>0.6277767282111801</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-2.330396851779077</v>
-      </c>
-      <c r="C96">
-        <v>0.8231730664237895</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.8909388413469903</v>
-      </c>
-      <c r="C97">
-        <v>-0.7371322776189758</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-1.395114017650686</v>
-      </c>
-      <c r="C98">
-        <v>-0.1454063716851109</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.7630829777615802</v>
-      </c>
-      <c r="C99">
-        <v>-0.6358790770711602</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>1.941343327494449</v>
-      </c>
-      <c r="C100">
-        <v>-2.459623318066792</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.619217411936211</v>
-      </c>
-      <c r="C101">
-        <v>-0.9443515009432455</v>
+        <v>0.3249075574789712</v>
       </c>
     </row>
   </sheetData>
